--- a/myprojects/GatiGo/BvsA/GatiGo_Dashboard.xlsx
+++ b/myprojects/GatiGo/BvsA/GatiGo_Dashboard.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\GitHub\inakm.github.io\myprojects\GatiGo\BvsA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1350" windowWidth="21570" windowHeight="9435" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="450" windowWidth="28800" windowHeight="13860" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="📊 KPI Dashboard" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="Assumptions (Budget)" sheetId="6" r:id="rId6"/>
     <sheet name="ℹ️ About" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <calcPr calcId="152511" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -1410,11 +1407,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2064,71 +2061,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="📈 KPI Dashboard"/>
-      <sheetName val="💡 Insights &amp; Recommendations"/>
-      <sheetName val="📊 Variance Analysis"/>
-      <sheetName val="📐 Unit Economics"/>
-      <sheetName val="🎯 Scenario Analysis"/>
-      <sheetName val="📋 Raw Data"/>
-      <sheetName val="ℹ️ About"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>January</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>February</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>March</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>Act NetProfit</v>
-          </cell>
-          <cell r="B24">
-            <v>-577265</v>
-          </cell>
-          <cell r="C24">
-            <v>-565671</v>
-          </cell>
-          <cell r="D24">
-            <v>-596040</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>Bud NetProfit</v>
-          </cell>
-          <cell r="B25">
-            <v>-555681</v>
-          </cell>
-          <cell r="C25">
-            <v>-533008</v>
-          </cell>
-          <cell r="D25">
-            <v>-509940</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3515,16 +3447,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="92" t="s">
@@ -3565,16 +3497,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -3745,16 +3677,16 @@
       <c r="H11" s="67"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
@@ -3922,16 +3854,16 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="99"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -4363,16 +4295,16 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="99" t="s">
+      <c r="A32" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="99"/>
-      <c r="C32" s="99"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="99"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
@@ -4580,16 +4512,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4760,16 +4692,16 @@
       <c r="H11" s="49"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98" t="s">
+      <c r="A12" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
@@ -4937,16 +4869,16 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="98" t="s">
+      <c r="A18" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="98"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -5378,16 +5310,16 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98" t="s">
+      <c r="A32" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="98"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="98"/>
-      <c r="E32" s="98"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="98"/>
-      <c r="H32" s="98"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="100"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
@@ -5504,16 +5436,16 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="98" t="s">
+      <c r="A38" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="B38" s="98"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="98"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="98"/>
-      <c r="H38" s="98"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="100"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="61" t="s">
